--- a/Data/JobChange/Workday_JobChange_Slovenia.xlsx
+++ b/Data/JobChange/Workday_JobChange_Slovenia.xlsx
@@ -133,7 +133,7 @@
   <si>
     <t xml:space="preserve">Test failed for 'Hyman Senger' Employee:{10700207}TimeoutError: locator.click: Timeout 30000ms exceeded.
 Call log:
-  [2m- waiting for getByRole('button', { name: 'Approve' })[22m
+  [2m- waiting for locator('//button[@aria-label=\'Edit Start Details\']')[22m
 </t>
   </si>
   <si>
@@ -167,7 +167,7 @@
     <t>Full Time</t>
   </si>
   <si>
-    <t>Auto 28257361</t>
+    <t>Auto 36725654</t>
   </si>
   <si>
     <t>Collective Agreement - Slovenia (01/01/1900 - )</t>
